--- a/90204_REPORT_BOTTEGA_06-01-2026.xlsx
+++ b/90204_REPORT_BOTTEGA_06-01-2026.xlsx
@@ -9,12 +9,13 @@
     <sheet name="VENDUTO FASCIA ORARIA" r:id="rId3" sheetId="1"/>
     <sheet name="ANALISI ARTICOLI" r:id="rId4" sheetId="2"/>
     <sheet name="PDT VENUTI FS GIORNALIERO" r:id="rId5" sheetId="3"/>
+    <sheet name="INGRESSI" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="102">
   <si>
     <t>FASCIA ORARIA</t>
   </si>
@@ -49,6 +50,39 @@
     <t>15:00 - 15:59</t>
   </si>
   <si>
+    <t>16:00 - 16:59</t>
+  </si>
+  <si>
+    <t>17:00 - 17:59</t>
+  </si>
+  <si>
+    <t>18:00 - 18:59</t>
+  </si>
+  <si>
+    <t>19:00 - 19:59</t>
+  </si>
+  <si>
+    <t>20:00 - 20:59</t>
+  </si>
+  <si>
+    <t>21:00 - 21:59</t>
+  </si>
+  <si>
+    <t>22:00 - 22:59</t>
+  </si>
+  <si>
+    <t>23:00 - 23:59</t>
+  </si>
+  <si>
+    <t>0:00 - 0:59</t>
+  </si>
+  <si>
+    <t>1:00 - 1:59</t>
+  </si>
+  <si>
+    <t>2:00 - 2:59</t>
+  </si>
+  <si>
     <t>TOTALE INCASSI 06/01/2026</t>
   </si>
   <si>
@@ -97,34 +131,70 @@
     <t>Stinco suino con patate</t>
   </si>
   <si>
+    <t>50-002-040-003750</t>
+  </si>
+  <si>
+    <t>Pulled pork con patate</t>
+  </si>
+  <si>
     <t>50-002-040-005280</t>
   </si>
   <si>
     <t>Hamburger B.A. con patate</t>
   </si>
   <si>
-    <t>50-002-040-003750</t>
-  </si>
-  <si>
-    <t>Pulled pork con patate</t>
-  </si>
-  <si>
     <t>50-002-040-005310</t>
   </si>
   <si>
     <t>Arrosticini</t>
   </si>
   <si>
+    <t>50-002-040-005130</t>
+  </si>
+  <si>
+    <t>Costata dal mondo 5,3</t>
+  </si>
+  <si>
+    <t>50-002-040-005380</t>
+  </si>
+  <si>
+    <t>Grigliata mista</t>
+  </si>
+  <si>
+    <t>50-002-040-003770</t>
+  </si>
+  <si>
+    <t>Patate</t>
+  </si>
+  <si>
+    <t>50-002-040-003390</t>
+  </si>
+  <si>
+    <t>Verdure</t>
+  </si>
+  <si>
+    <t>50-002-040-003320</t>
+  </si>
+  <si>
+    <t>B1 Battuta A Coltello Ba</t>
+  </si>
+  <si>
     <t>50-002-040-005420</t>
   </si>
   <si>
     <t>Fiorentina con filetto al kg</t>
   </si>
   <si>
-    <t>50-002-040-003390</t>
-  </si>
-  <si>
-    <t>Verdure</t>
+    <t>50-002-040-005330</t>
+  </si>
+  <si>
+    <t>Spiedini misti</t>
+  </si>
+  <si>
+    <t>50-002-040-003611</t>
+  </si>
+  <si>
+    <t>Prosciutto Dolce O Saporito Affettato</t>
   </si>
   <si>
     <t>50-002-040-003850</t>
@@ -133,10 +203,22 @@
     <t>Grigliata mista bovino</t>
   </si>
   <si>
-    <t>50-002-040-003770</t>
-  </si>
-  <si>
-    <t>Patate</t>
+    <t>50-002-040-003615</t>
+  </si>
+  <si>
+    <t>Salame Di Prosciutto Pezzo/Intero</t>
+  </si>
+  <si>
+    <t>50-002-040-005390</t>
+  </si>
+  <si>
+    <t>Grigliata mista XXL</t>
+  </si>
+  <si>
+    <t>50-002-040-005440</t>
+  </si>
+  <si>
+    <t>Tagliata di pollo</t>
   </si>
   <si>
     <t>50-002-040-003240</t>
@@ -151,18 +233,24 @@
     <t>Filetto B.A. 220g</t>
   </si>
   <si>
+    <t>50-002-040-003640</t>
+  </si>
+  <si>
+    <t>Costata B.A.</t>
+  </si>
+  <si>
+    <t>50-002-040-003630</t>
+  </si>
+  <si>
+    <t>Etrusca Marin Alla Birra Di Castag 300g</t>
+  </si>
+  <si>
     <t>50-002-040-003596</t>
   </si>
   <si>
     <t>Finocchiona Cinta Piccola Pezzo/Intero</t>
   </si>
   <si>
-    <t>50-002-040-005380</t>
-  </si>
-  <si>
-    <t>Grigliata mista</t>
-  </si>
-  <si>
     <t>50-002-040-005270</t>
   </si>
   <si>
@@ -175,22 +263,22 @@
     <t>Aggiunta Contorno</t>
   </si>
   <si>
-    <t>50-002-040-005330</t>
-  </si>
-  <si>
-    <t>Spiedini misti</t>
-  </si>
-  <si>
-    <t>50-002-040-003320</t>
-  </si>
-  <si>
-    <t>B1 Battuta A Coltello Ba</t>
-  </si>
-  <si>
-    <t>50-002-040-003615</t>
-  </si>
-  <si>
-    <t>Salame Di Prosciutto Pezzo/Intero</t>
+    <t>50-002-040-005300</t>
+  </si>
+  <si>
+    <t>hamburger di suino con patate</t>
+  </si>
+  <si>
+    <t>50-002-040-003619</t>
+  </si>
+  <si>
+    <t>Salsiccia Passita Cinta  Pezzo/Intero</t>
+  </si>
+  <si>
+    <t>50-002-040-003616</t>
+  </si>
+  <si>
+    <t>Salame Montanaro Pezzo/Intero</t>
   </si>
   <si>
     <t>50-002-040-003576</t>
@@ -199,6 +287,12 @@
     <t>Hamburger B.A.</t>
   </si>
   <si>
+    <t>50-002-040-003635</t>
+  </si>
+  <si>
+    <t>Cipolle In Agrodolce</t>
+  </si>
+  <si>
     <t>TOTALE GRUPPO</t>
   </si>
   <si>
@@ -212,6 +306,21 @@
   </si>
   <si>
     <t>12:00-15:59</t>
+  </si>
+  <si>
+    <t>16:00-18:59</t>
+  </si>
+  <si>
+    <t>19:00-02:59</t>
+  </si>
+  <si>
+    <t>06/01/2026</t>
+  </si>
+  <si>
+    <t>VAR %</t>
+  </si>
+  <si>
+    <t>06/01/2025</t>
   </si>
 </sst>
 </file>
@@ -349,7 +458,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true"/>
@@ -362,13 +471,27 @@
     <xf numFmtId="4" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.59375" customWidth="true" bestFit="true"/>
@@ -456,27 +579,115 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="1">
+      <c r="A11" t="s" s="2">
         <v>11</v>
       </c>
-      <c r="B11" t="n" s="1">
-        <v>1626.32</v>
+      <c r="B11" t="n" s="5">
+        <v>208.3363</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="1">
+      <c r="A12" t="s" s="4">
         <v>12</v>
       </c>
-      <c r="B12" t="n" s="1">
-        <v>1450.53</v>
+      <c r="B12" t="n" s="7">
+        <v>148.9546</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s" s="1">
+      <c r="A13" t="s" s="2">
         <v>13</v>
       </c>
-      <c r="B13" t="n" s="1">
-        <v>12.12</v>
+      <c r="B13" t="n" s="5">
+        <v>306.991</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="4">
+        <v>14</v>
+      </c>
+      <c r="B14" t="n" s="7">
+        <v>129.8182</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B15" t="n" s="5">
+        <v>227.5638</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="4">
+        <v>16</v>
+      </c>
+      <c r="B16" t="n" s="7">
+        <v>80.7273</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B17" t="n" s="5">
+        <v>34.4546</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="4">
+        <v>18</v>
+      </c>
+      <c r="B18" t="n" s="7">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B19" t="n" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="B20" t="n" s="7">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B21" t="n" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="B22" t="n" s="1">
+        <v>2763.16</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="1">
+        <v>23</v>
+      </c>
+      <c r="B23" t="n" s="1">
+        <v>2397.3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="B24" t="n" s="1">
+        <v>15.26</v>
       </c>
     </row>
   </sheetData>
@@ -486,11 +697,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="36.234375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="37.29296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.81640625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="17.91796875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="7.72265625" customWidth="true" bestFit="true"/>
@@ -498,390 +709,560 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="4">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C2" t="n" s="7">
-        <v>379.0909</v>
+        <v>515.4546</v>
       </c>
       <c r="D2" t="n" s="7">
-        <v>28.0</v>
+        <v>38.0</v>
       </c>
       <c r="E2" t="n" s="7">
-        <v>23.31</v>
+        <v>18.65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C3" t="n" s="5">
-        <v>327.2726</v>
+        <v>509.0908</v>
       </c>
       <c r="D3" t="n" s="5">
-        <v>18.0</v>
+        <v>28.0</v>
       </c>
       <c r="E3" t="n" s="5">
-        <v>20.12</v>
+        <v>18.42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C4" t="n" s="7">
-        <v>227.8182</v>
+        <v>358.0002</v>
       </c>
       <c r="D4" t="n" s="7">
-        <v>14.0</v>
+        <v>22.0</v>
       </c>
       <c r="E4" t="n" s="7">
-        <v>14.01</v>
+        <v>12.96</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C5" t="n" s="5">
-        <v>158.9999</v>
+        <v>173.4544</v>
       </c>
       <c r="D5" t="n" s="5">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E5" t="n" s="5">
-        <v>9.78</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n" s="7">
-        <v>113.7273</v>
+        <v>169.9998</v>
       </c>
       <c r="D6" t="n" s="7">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="E6" t="n" s="7">
-        <v>6.99</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C7" t="n" s="5">
-        <v>77.2726</v>
+        <v>151.6365</v>
       </c>
       <c r="D7" t="n" s="5">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="E7" t="n" s="5">
-        <v>4.75</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C8" t="n" s="7">
-        <v>65.4546</v>
+        <v>114.5454</v>
       </c>
       <c r="D8" t="n" s="7">
-        <v>61.0</v>
+        <v>106.0</v>
       </c>
       <c r="E8" t="n" s="7">
-        <v>4.02</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n" s="5">
-        <v>57.3909</v>
+        <v>105.8091</v>
       </c>
       <c r="D9" t="n" s="5">
-        <v>1.07</v>
+        <v>2.2</v>
       </c>
       <c r="E9" t="n" s="5">
-        <v>3.53</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n" s="7">
-        <v>45.4546</v>
+        <v>72.2726</v>
       </c>
       <c r="D10" t="n" s="7">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="E10" t="n" s="7">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n" s="5">
-        <v>27.2727</v>
+        <v>65.4546</v>
       </c>
       <c r="D11" t="n" s="5">
-        <v>1.0</v>
+        <v>18.0</v>
       </c>
       <c r="E11" t="n" s="5">
-        <v>1.68</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C12" t="n" s="7">
-        <v>21.8182</v>
+        <v>63.6366</v>
       </c>
       <c r="D12" t="n" s="7">
-        <v>6.0</v>
+        <v>14.0</v>
       </c>
       <c r="E12" t="n" s="7">
-        <v>1.34</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C13" t="n" s="5">
-        <v>19.8182</v>
+        <v>62.7454</v>
       </c>
       <c r="D13" t="n" s="5">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="E13" t="n" s="5">
-        <v>1.22</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="4">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C14" t="n" s="7">
-        <v>19.0909</v>
+        <v>57.3909</v>
       </c>
       <c r="D14" t="n" s="7">
-        <v>1.0</v>
+        <v>1.07</v>
       </c>
       <c r="E14" t="n" s="7">
-        <v>1.17</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C15" t="n" s="5">
-        <v>14.5818</v>
+        <v>54.0909</v>
       </c>
       <c r="D15" t="n" s="5">
-        <v>0.4</v>
+        <v>5.0</v>
       </c>
       <c r="E15" t="n" s="5">
-        <v>0.9</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s" s="4">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C16" t="n" s="7">
-        <v>14.4545</v>
+        <v>45.6727</v>
       </c>
       <c r="D16" t="n" s="7">
-        <v>1.0</v>
+        <v>1.03</v>
       </c>
       <c r="E16" t="n" s="7">
-        <v>0.89</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C17" t="n" s="5">
-        <v>13.6364</v>
+        <v>27.2727</v>
       </c>
       <c r="D17" t="n" s="5">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="E17" t="n" s="5">
-        <v>0.84</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s" s="4">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C18" t="n" s="7">
-        <v>10.9092</v>
+        <v>26.0272</v>
       </c>
       <c r="D18" t="n" s="7">
-        <v>12.0</v>
+        <v>0.73</v>
       </c>
       <c r="E18" t="n" s="7">
-        <v>0.67</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C19" t="n" s="5">
-        <v>10.8182</v>
+        <v>23.5455</v>
       </c>
       <c r="D19" t="n" s="5">
         <v>1.0</v>
       </c>
       <c r="E19" t="n" s="5">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="4">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s" s="4">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C20" t="n" s="7">
-        <v>8.6545</v>
+        <v>23.4546</v>
       </c>
       <c r="D20" t="n" s="7">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E20" t="n" s="7">
-        <v>0.53</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C21" t="n" s="5">
-        <v>7.8727</v>
+        <v>19.8182</v>
       </c>
       <c r="D21" t="n" s="5">
-        <v>0.22</v>
+        <v>2.0</v>
       </c>
       <c r="E21" t="n" s="5">
-        <v>0.48</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="4">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s" s="4">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C22" t="n" s="7">
+        <v>19.0909</v>
+      </c>
+      <c r="D22" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="E22" t="n" s="7">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C23" t="n" s="5">
+        <v>16.5</v>
+      </c>
+      <c r="D23" t="n" s="5">
+        <v>0.51</v>
+      </c>
+      <c r="E23" t="n" s="5">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="4">
+        <v>74</v>
+      </c>
+      <c r="B24" t="s" s="4">
+        <v>75</v>
+      </c>
+      <c r="C24" t="n" s="7">
+        <v>15.3636</v>
+      </c>
+      <c r="D24" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="E24" t="n" s="7">
+        <v>0.56</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="C25" t="n" s="5">
+        <v>14.5818</v>
+      </c>
+      <c r="D25" t="n" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="E25" t="n" s="5">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="4">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s" s="4">
+        <v>79</v>
+      </c>
+      <c r="C26" t="n" s="7">
+        <v>13.6364</v>
+      </c>
+      <c r="D26" t="n" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="E26" t="n" s="7">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="C27" t="n" s="5">
+        <v>12.7274</v>
+      </c>
+      <c r="D27" t="n" s="5">
+        <v>14.0</v>
+      </c>
+      <c r="E27" t="n" s="5">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="4">
+        <v>82</v>
+      </c>
+      <c r="B28" t="s" s="4">
+        <v>83</v>
+      </c>
+      <c r="C28" t="n" s="7">
+        <v>11.7273</v>
+      </c>
+      <c r="D28" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="E28" t="n" s="7">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C29" t="n" s="5">
+        <v>5.6</v>
+      </c>
+      <c r="D29" t="n" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="E29" t="n" s="5">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="4">
+        <v>86</v>
+      </c>
+      <c r="B30" t="s" s="4">
+        <v>87</v>
+      </c>
+      <c r="C30" t="n" s="7">
+        <v>5.1091</v>
+      </c>
+      <c r="D30" t="n" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="E30" t="n" s="7">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="C31" t="n" s="5">
         <v>4.9091</v>
       </c>
-      <c r="D22" t="n" s="7">
+      <c r="D31" t="n" s="5">
         <v>0.31</v>
       </c>
-      <c r="E22" t="n" s="7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="1">
-        <v>61</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" t="n" s="1">
-        <v>1626.32</v>
-      </c>
-      <c r="D23" t="n" s="1">
-        <v>186.0</v>
-      </c>
-      <c r="E23" t="n" s="1">
+      <c r="E31" t="n" s="5">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="4">
+        <v>90</v>
+      </c>
+      <c r="B32" t="s" s="4">
+        <v>91</v>
+      </c>
+      <c r="C32" t="n" s="7">
+        <v>4.5455</v>
+      </c>
+      <c r="D32" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="E32" t="n" s="7">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="1">
+        <v>92</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" t="n" s="1">
+        <v>2763.16</v>
+      </c>
+      <c r="D33" t="n" s="1">
+        <v>310.61</v>
+      </c>
+      <c r="E33" t="n" s="1">
         <v>100.0</v>
       </c>
     </row>
@@ -892,24 +1273,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="36.234375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="37.29296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="17.91796875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="31.40625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -917,15 +1298,15 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="1">
-        <v>62</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C3" t="n" s="5">
         <v>10.0</v>
@@ -936,10 +1317,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C4" t="n" s="7">
         <v>3.0</v>
@@ -950,10 +1331,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C5" t="n" s="5">
         <v>3.0</v>
@@ -964,10 +1345,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C6" t="n" s="7">
         <v>2.0</v>
@@ -978,10 +1359,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C7" t="n" s="5">
         <v>1.0</v>
@@ -992,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C8" t="n" s="7">
         <v>1.0</v>
@@ -1006,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n" s="5">
         <v>1.0</v>
@@ -1020,10 +1401,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n" s="7">
         <v>1.0</v>
@@ -1034,10 +1415,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n" s="5">
         <v>1.0</v>
@@ -1048,10 +1429,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="C12" t="n" s="7">
         <v>0.4</v>
@@ -1062,10 +1443,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C13" t="n" s="5">
         <v>0.22</v>
@@ -1076,10 +1457,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="1">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="C14" t="n" s="1">
         <v>23.62</v>
@@ -1091,15 +1472,15 @@
     <row r="15"/>
     <row r="16">
       <c r="A16" t="s" s="1">
-        <v>65</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C17" t="n" s="5">
         <v>61.0</v>
@@ -1110,10 +1491,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s" s="4">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C18" t="n" s="7">
         <v>18.0</v>
@@ -1124,10 +1505,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C19" t="n" s="5">
         <v>16.0</v>
@@ -1138,10 +1519,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="4">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s" s="4">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C20" t="n" s="7">
         <v>13.0</v>
@@ -1152,10 +1533,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C21" t="n" s="5">
         <v>10.0</v>
@@ -1166,10 +1547,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="4">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="B22" t="s" s="4">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C22" t="n" s="7">
         <v>9.0</v>
@@ -1180,10 +1561,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C23" t="n" s="5">
         <v>8.0</v>
@@ -1194,10 +1575,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="4">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B24" t="s" s="4">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C24" t="n" s="7">
         <v>8.0</v>
@@ -1208,10 +1589,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C25" t="n" s="5">
         <v>5.0</v>
@@ -1222,10 +1603,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="4">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s" s="4">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C26" t="n" s="7">
         <v>5.0</v>
@@ -1236,10 +1617,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="C27" t="n" s="5">
         <v>3.0</v>
@@ -1250,10 +1631,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="4">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s" s="4">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="C28" t="n" s="7">
         <v>1.07</v>
@@ -1264,10 +1645,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C29" t="n" s="5">
         <v>1.0</v>
@@ -1278,10 +1659,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="4">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="B30" t="s" s="4">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C30" t="n" s="7">
         <v>1.0</v>
@@ -1292,10 +1673,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>48</v>
       </c>
       <c r="C31" t="n" s="5">
         <v>1.0</v>
@@ -1306,10 +1687,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="4">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B32" t="s" s="4">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="C32" t="n" s="7">
         <v>1.0</v>
@@ -1320,10 +1701,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C33" t="n" s="5">
         <v>1.0</v>
@@ -1334,10 +1715,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="4">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="B34" t="s" s="4">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C34" t="n" s="7">
         <v>0.31</v>
@@ -1348,10 +1729,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="1">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="C35" t="n" s="1">
         <v>162.38</v>
@@ -1361,13 +1742,571 @@
       </c>
     </row>
     <row r="36"/>
+    <row r="37">
+      <c r="A37" t="s" s="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="B38" t="s" s="4">
+        <v>43</v>
+      </c>
+      <c r="C38" t="n" s="7">
+        <v>10.0</v>
+      </c>
+      <c r="D38" t="n" s="7">
+        <v>10.909</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="C39" t="n" s="5">
+        <v>7.0</v>
+      </c>
+      <c r="D39" t="n" s="5">
+        <v>127.2728</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="4">
+        <v>30</v>
+      </c>
+      <c r="B40" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="C40" t="n" s="7">
+        <v>7.0</v>
+      </c>
+      <c r="D40" t="n" s="7">
+        <v>95.4546</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="C41" t="n" s="5">
+        <v>6.0</v>
+      </c>
+      <c r="D41" t="n" s="5">
+        <v>21.8182</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="4">
+        <v>34</v>
+      </c>
+      <c r="B42" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="C42" t="n" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="D42" t="n" s="7">
+        <v>65.091</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="C43" t="n" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="D43" t="n" s="5">
+        <v>43.2727</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="4">
+        <v>38</v>
+      </c>
+      <c r="B44" t="s" s="4">
+        <v>39</v>
+      </c>
+      <c r="C44" t="n" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="D44" t="n" s="7">
+        <v>46.3636</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="C45" t="n" s="5">
+        <v>2.2</v>
+      </c>
+      <c r="D45" t="n" s="5">
+        <v>105.8091</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="4">
+        <v>50</v>
+      </c>
+      <c r="B46" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="C46" t="n" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="D46" t="n" s="7">
+        <v>9.091</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="C47" t="n" s="5">
+        <v>1.03</v>
+      </c>
+      <c r="D47" t="n" s="5">
+        <v>45.6727</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="4">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s" s="4">
+        <v>47</v>
+      </c>
+      <c r="C48" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D48" t="n" s="7">
+        <v>14.4545</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C49" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D49" t="n" s="5">
+        <v>14.4545</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="B50" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C50" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D50" t="n" s="7">
+        <v>12.6364</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="C51" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D51" t="n" s="5">
+        <v>11.7273</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="4">
+        <v>62</v>
+      </c>
+      <c r="B52" t="s" s="4">
+        <v>63</v>
+      </c>
+      <c r="C52" t="n" s="7">
+        <v>0.51</v>
+      </c>
+      <c r="D52" t="n" s="7">
+        <v>18.1545</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C53" t="n" s="5">
+        <v>0.51</v>
+      </c>
+      <c r="D53" t="n" s="5">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="4">
+        <v>84</v>
+      </c>
+      <c r="B54" t="s" s="4">
+        <v>85</v>
+      </c>
+      <c r="C54" t="n" s="7">
+        <v>0.21</v>
+      </c>
+      <c r="D54" t="n" s="7">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="1">
+        <v>94</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="C55" t="n" s="1">
+        <v>51.46</v>
+      </c>
+      <c r="D55" t="n" s="1">
+        <v>664.28</v>
+      </c>
+    </row>
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" t="s" s="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="4">
+        <v>42</v>
+      </c>
+      <c r="B58" t="s" s="4">
+        <v>43</v>
+      </c>
+      <c r="C58" t="n" s="7">
+        <v>35.0</v>
+      </c>
+      <c r="D58" t="n" s="7">
+        <v>38.1818</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="C59" t="n" s="5">
+        <v>6.0</v>
+      </c>
+      <c r="D59" t="n" s="5">
+        <v>21.8182</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="4">
+        <v>52</v>
+      </c>
+      <c r="B60" t="s" s="4">
+        <v>53</v>
+      </c>
+      <c r="C60" t="n" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="D60" t="n" s="7">
+        <v>54.0909</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="C61" t="n" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="D61" t="n" s="5">
+        <v>65.091</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="4">
+        <v>32</v>
+      </c>
+      <c r="B62" t="s" s="4">
+        <v>33</v>
+      </c>
+      <c r="C62" t="n" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="D62" t="n" s="7">
+        <v>54.5454</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C63" t="n" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="D63" t="n" s="5">
+        <v>46.3636</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="4">
+        <v>46</v>
+      </c>
+      <c r="B64" t="s" s="4">
+        <v>47</v>
+      </c>
+      <c r="C64" t="n" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="D64" t="n" s="7">
+        <v>43.3636</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C65" t="n" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="D65" t="n" s="5">
+        <v>40.9091</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="B66" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C66" t="n" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="D66" t="n" s="7">
+        <v>25.2728</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="C67" t="n" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="D67" t="n" s="5">
+        <v>9.091</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="4">
+        <v>80</v>
+      </c>
+      <c r="B68" t="s" s="4">
+        <v>81</v>
+      </c>
+      <c r="C68" t="n" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="D68" t="n" s="7">
+        <v>1.8182</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="C69" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D69" t="n" s="5">
+        <v>23.5455</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="4">
+        <v>74</v>
+      </c>
+      <c r="B70" t="s" s="4">
+        <v>75</v>
+      </c>
+      <c r="C70" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D70" t="n" s="7">
+        <v>15.3636</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C71" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D71" t="n" s="5">
+        <v>11.7273</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="4">
+        <v>66</v>
+      </c>
+      <c r="B72" t="s" s="4">
+        <v>67</v>
+      </c>
+      <c r="C72" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D72" t="n" s="7">
+        <v>11.7273</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="C73" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D73" t="n" s="5">
+        <v>4.5455</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="4">
+        <v>86</v>
+      </c>
+      <c r="B74" t="s" s="4">
+        <v>87</v>
+      </c>
+      <c r="C74" t="n" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="D74" t="n" s="7">
+        <v>5.1091</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="1">
+        <v>94</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="C75" t="n" s="1">
+        <v>73.15</v>
+      </c>
+      <c r="D75" t="n" s="1">
+        <v>472.56</v>
+      </c>
+    </row>
+    <row r="76"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="A75:B75"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="12.73046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="7.9140625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.73046875" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>99</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>100</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="9">
+        <v>8285.0</v>
+      </c>
+      <c r="B2" s="12" t="n">
+        <f>(A2-C2)/C2</f>
+        <v>0.0</v>
+      </c>
+      <c r="C2" t="n" s="9">
+        <v>8072.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>